--- a/lab3/I14243.xlsx
+++ b/lab3/I14243.xlsx
@@ -1,21 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/magdalenasmietana/Documents/Fizyka/Fizyka-Lab/lab3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dkomeza/Desktop/Fizyka-Lab/lab3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C4800E-3F9B-4C41-B804-01B1B84EAC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C186806F-6C01-1245-BA06-DAE97DF8BFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{57C4C638-7895-C144-878A-17F30D214164}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{57C4C638-7895-C144-878A-17F30D214164}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$12</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$A$13</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$B$10:$L$10</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$B$12:$L$12</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$B$13:$L$13</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$B$14:$L$14</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$A$12</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$A$13</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$A$14</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$B$10:$L$10</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$B$12:$L$12</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$B$13:$L$13</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$A$14</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$B$14:$L$14</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$10:$L$10</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$12:$L$12</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$13:$L$13</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$B$14:$L$14</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$A$12</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$A$13</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$A$14</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +50,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -34,8 +58,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>liczba zwojów</t>
   </si>
@@ -81,6 +127,30 @@
   <si>
     <t>I_s</t>
   </si>
+  <si>
+    <t>Indukcja cewki [mT]</t>
+  </si>
+  <si>
+    <t>a_5</t>
+  </si>
+  <si>
+    <t>a_10</t>
+  </si>
+  <si>
+    <t>a_14</t>
+  </si>
+  <si>
+    <t>c_5</t>
+  </si>
+  <si>
+    <t>c_10</t>
+  </si>
+  <si>
+    <t>c_14</t>
+  </si>
+  <si>
+    <t>c_avg</t>
+  </si>
 </sst>
 </file>
 
@@ -115,12 +185,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -153,6 +224,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Wykres</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> napięcia U halotronu w zależności od prądu I</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -185,8 +286,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -203,10 +304,8 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -226,7 +325,58 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:cat>
+          <c:trendline>
+            <c:name>5mA</c:name>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.80189752764321065"/>
+                  <c:y val="0.16710033339621605"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$10:$L$10</c:f>
               <c:numCache>
@@ -267,8 +417,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Sheet1!$B$12:$L$12</c:f>
               <c:numCache>
@@ -309,7 +459,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -332,10 +482,8 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -355,7 +503,58 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:cat>
+          <c:trendline>
+            <c:name>10mA</c:name>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.77493298041152525"/>
+                  <c:y val="0.33677013553492352"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$10:$L$10</c:f>
               <c:numCache>
@@ -396,8 +595,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Sheet1!$B$13:$L$13</c:f>
               <c:numCache>
@@ -438,7 +637,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -461,10 +660,8 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -484,7 +681,58 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:cat>
+          <c:trendline>
+            <c:name>14mA</c:name>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.78392116282208701"/>
+                  <c:y val="0.58921880406284755"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$10:$L$10</c:f>
               <c:numCache>
@@ -525,8 +773,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Sheet1!$B$14:$L$14</c:f>
               <c:numCache>
@@ -567,7 +815,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -583,22 +831,35 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
         <c:axId val="1405567424"/>
         <c:axId val="1405580864"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="1405567424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="10"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="low"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -634,11 +895,8 @@
         </c:txPr>
         <c:crossAx val="1405580864"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="1405580864"/>
         <c:scaling>
@@ -693,12 +951,14 @@
         </c:txPr>
         <c:crossAx val="1405567424"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -736,6 +996,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -743,7 +1004,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1325,16 +1585,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>69850</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1353</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>27018</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>146050</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>776941</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1363,9 +1623,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1403,7 +1663,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1509,7 +1769,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1651,7 +1911,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1659,12 +1919,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1B0C41-3D00-5C47-9F63-8AE535CBD2C7}">
-  <dimension ref="A2:W41"/>
+  <dimension ref="A2:W44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1741,19 +2002,19 @@
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -1869,298 +2130,617 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <f>B12/1000</f>
+        <v>-1.4499999999999999E-3</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:L15" si="0">C12/1000</f>
+        <v>-1.06E-3</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>-6.7000000000000002E-4</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>-2.5000000000000001E-4</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>1.1999999999999999E-4</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>8.7000000000000001E-4</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>1.2600000000000001E-3</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>1.64E-3</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>2.0099999999999996E-3</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="0"/>
+        <v>2.3700000000000001E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <f t="shared" ref="B16:L16" si="1">B13/1000</f>
+        <v>-4.7000000000000002E-3</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>-3.8E-3</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>-3.2000000000000002E-3</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>-2.4199999999999998E-3</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>-1.6000000000000001E-3</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>-8.1999999999999998E-4</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>-1E-4</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>1.2600000000000001E-3</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>2E-3</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>2.7499999999999998E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <f t="shared" ref="B17:L17" si="2">B14/1000</f>
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="2"/>
+        <v>-4.3E-3</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>-3.4300000000000003E-3</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>-2.4500000000000004E-3</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>-1.3799999999999999E-3</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>-4.4999999999999999E-4</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>1.5499999999999999E-3</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="2"/>
+        <v>2.5499999999999997E-3</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>3.5600000000000002E-3</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>4.5199999999999997E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * B10) / ($B$3) * 1000</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="3">
+        <f t="shared" ref="C18:L18" si="3" xml:space="preserve"> (4*PI()*10^-7 * $A$3 * C10) / ($B$3) * 1000</f>
+        <v>7.9967813000467473E-4</v>
+      </c>
+      <c r="D18" s="3">
+        <f t="shared" si="3"/>
+        <v>1.5993562600093495E-3</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="3"/>
+        <v>2.3990343900140237E-3</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="3"/>
+        <v>3.1987125200186989E-3</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="3"/>
+        <v>3.9983906500233729E-3</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="3"/>
+        <v>4.7980687800280473E-3</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="3"/>
+        <v>5.5977469100327226E-3</v>
+      </c>
+      <c r="J18" s="3">
+        <f t="shared" si="3"/>
+        <v>6.3174572270369303E-3</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="3"/>
+        <v>7.0371675440411372E-3</v>
+      </c>
+      <c r="L18" s="3">
+        <f t="shared" si="3"/>
+        <v>7.7568778610453441E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25">
+        <f>SLOPE(B12:L12,$B$18:$L$18)</f>
+        <v>489.84703443408409</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25">
+        <f>B25/A12</f>
+        <v>97.969406886816813</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26">
+        <f>SLOPE(B13:L13,$B$18:$L$18)</f>
+        <v>945.84212420725271</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <f>B26/A13</f>
+        <v>94.584212420725265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27">
+        <f>SLOPE(B14:L14,$B$18:$L$18)</f>
+        <v>1302.8528664306698</v>
+      </c>
+      <c r="C27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27">
+        <f>B27/A14</f>
+        <v>93.060919030762122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28">
+        <f>AVERAGE(D25:D27)</f>
+        <v>95.204846112768067</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" cm="1">
+        <f t="array" ref="B30:C30">LINEST(B15:L15,$B$10:$L$10,TRUE,FALSE)</f>
+        <v>3.917199604845838E-4</v>
+      </c>
+      <c r="C30">
+        <v>-1.4517787136692148E-3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30">
+        <f>B30/A12</f>
+        <v>7.8343992096916763E-5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" cm="1">
+        <f t="array" ref="B31:C31">LINEST(B16:L16,$B$10:$L$10,TRUE,FALSE)</f>
+        <v>7.5636926116570485E-4</v>
+      </c>
+      <c r="C31">
+        <v>-4.6578625279467588E-3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31">
+        <f t="shared" ref="E31:E32" si="4">B31/A13</f>
+        <v>7.5636926116570482E-5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" cm="1">
+        <f t="array" ref="B32:C32">LINEST(B17:L17,$B$10:$L$10,TRUE,FALSE)</f>
+        <v>1.0418629438985077E-3</v>
+      </c>
+      <c r="C32">
+        <v>-5.6324858316435305E-3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="4"/>
+        <v>7.4418781707036264E-5</v>
+      </c>
+    </row>
     <row r="33" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="S33" t="s">
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33">
+        <f>AVERAGE(E30:E32)</f>
+        <v>7.613323330684117E-5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="S36" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
         <v>7</v>
       </c>
-      <c r="C34">
+      <c r="C37">
         <v>0</v>
       </c>
-      <c r="D34">
+      <c r="D37">
         <v>0.5</v>
       </c>
-      <c r="E34">
+      <c r="E37">
         <v>1</v>
       </c>
-      <c r="F34">
+      <c r="F37">
         <v>1.5</v>
       </c>
-      <c r="G34">
+      <c r="G37">
         <v>2</v>
       </c>
-      <c r="H34">
+      <c r="H37">
         <v>2.5</v>
       </c>
-      <c r="I34">
+      <c r="I37">
         <v>3</v>
       </c>
-      <c r="J34">
+      <c r="J37">
         <v>3.5</v>
       </c>
-      <c r="K34">
+      <c r="K37">
         <v>4</v>
       </c>
-      <c r="L34">
+      <c r="L37">
         <v>4.5</v>
       </c>
-      <c r="M34">
+      <c r="M37">
         <v>5</v>
       </c>
-      <c r="N34">
+      <c r="N37">
         <v>5.5</v>
       </c>
-      <c r="O34">
+      <c r="O37">
         <v>6</v>
       </c>
-      <c r="P34">
+      <c r="P37">
         <v>6.5</v>
       </c>
-      <c r="Q34">
+      <c r="Q37">
         <v>7</v>
       </c>
-      <c r="R34">
+      <c r="R37">
         <v>7.5</v>
       </c>
-      <c r="S34">
+      <c r="S37">
         <v>8</v>
       </c>
-      <c r="T34">
+      <c r="T37">
         <v>8.5</v>
       </c>
-      <c r="U34">
+      <c r="U37">
         <v>9</v>
       </c>
-      <c r="V34">
+      <c r="V37">
         <v>9.5</v>
       </c>
-      <c r="W34">
+      <c r="W37">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C35">
+      <c r="C38">
         <v>3.15</v>
       </c>
-      <c r="D35">
+      <c r="D38">
         <v>2.95</v>
       </c>
-      <c r="E35">
+      <c r="E38">
         <v>2.61</v>
       </c>
-      <c r="F35">
+      <c r="F38">
         <v>2.02</v>
       </c>
-      <c r="G35">
+      <c r="G38">
         <v>1.41</v>
       </c>
-      <c r="H35">
+      <c r="H38">
         <v>0.68</v>
       </c>
-      <c r="I35">
+      <c r="I38">
         <v>-0.12</v>
       </c>
-      <c r="J35">
+      <c r="J38">
         <v>-0.85</v>
       </c>
-      <c r="K35">
+      <c r="K38">
         <v>-1.5</v>
       </c>
-      <c r="L35">
+      <c r="L38">
         <v>-2.15</v>
       </c>
-      <c r="M35">
+      <c r="M38">
         <v>-2.78</v>
       </c>
-      <c r="N35">
+      <c r="N38">
         <v>-3.31</v>
       </c>
-      <c r="O35">
+      <c r="O38">
         <f>--3.78</f>
         <v>3.78</v>
       </c>
-      <c r="P35">
+      <c r="P38">
         <v>-4.1900000000000004</v>
       </c>
-      <c r="Q35">
+      <c r="Q38">
         <v>-4.55</v>
       </c>
-      <c r="R35">
+      <c r="R38">
         <v>-4.84</v>
       </c>
-      <c r="S35">
+      <c r="S38">
         <v>-5.07</v>
       </c>
-      <c r="T35">
+      <c r="T38">
         <v>-4.2</v>
       </c>
-      <c r="U35">
+      <c r="U38">
         <v>-4.25</v>
       </c>
-      <c r="V35">
+      <c r="V38">
         <v>-4.4000000000000004</v>
       </c>
-      <c r="W35">
+      <c r="W38">
         <v>-4.45</v>
-      </c>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="2">
-        <f>$C$37/POWER(1+(POWER(C34/100, 2)/POWER($C$40, 2)), 1.5)</f>
-        <v>7.7568778610453437</v>
-      </c>
-      <c r="D36" s="2">
-        <f t="shared" ref="D36:W36" si="0">$C$37/POWER(1+(POWER(D34/100, 2)/POWER($C$40, 2)), 1.5)</f>
-        <v>7.6617021130409011</v>
-      </c>
-      <c r="E36" s="2">
-        <f t="shared" si="0"/>
-        <v>7.3875424446409612</v>
-      </c>
-      <c r="F36" s="2">
-        <f t="shared" si="0"/>
-        <v>6.9654628481359468</v>
-      </c>
-      <c r="G36" s="2">
-        <f t="shared" si="0"/>
-        <v>6.4384919625856183</v>
-      </c>
-      <c r="H36" s="2">
-        <f t="shared" si="0"/>
-        <v>5.8524232226751316</v>
-      </c>
-      <c r="I36" s="2">
-        <f t="shared" si="0"/>
-        <v>5.2482622725844976</v>
-      </c>
-      <c r="J36" s="2">
-        <f t="shared" si="0"/>
-        <v>4.6579157240299827</v>
-      </c>
-      <c r="K36" s="2">
-        <f t="shared" si="0"/>
-        <v>4.1030557316699907</v>
-      </c>
-      <c r="L36" s="2">
-        <f t="shared" si="0"/>
-        <v>3.5961512920284524</v>
-      </c>
-      <c r="M36" s="2">
-        <f t="shared" si="0"/>
-        <v>3.1425094915513876</v>
-      </c>
-      <c r="N36" s="2">
-        <f t="shared" si="0"/>
-        <v>2.7424704681904823</v>
-      </c>
-      <c r="O36" s="2">
-        <f t="shared" si="0"/>
-        <v>2.393294802808394</v>
-      </c>
-      <c r="P36" s="2">
-        <f t="shared" si="0"/>
-        <v>2.0905858750120658</v>
-      </c>
-      <c r="Q36" s="2">
-        <f t="shared" si="0"/>
-        <v>1.8292628533410984</v>
-      </c>
-      <c r="R36" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6041717368106754</v>
-      </c>
-      <c r="S36" s="2">
-        <f t="shared" si="0"/>
-        <v>1.410434697484104</v>
-      </c>
-      <c r="T36" s="2">
-        <f t="shared" si="0"/>
-        <v>1.2436243690615909</v>
-      </c>
-      <c r="U36" s="2">
-        <f t="shared" si="0"/>
-        <v>1.0998285575528679</v>
-      </c>
-      <c r="V36" s="2">
-        <f t="shared" si="0"/>
-        <v>0.97565090394196352</v>
-      </c>
-      <c r="W36" s="2">
-        <f t="shared" si="0"/>
-        <v>0.86817729480338701</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37">
-        <f>(4 * PI() * POWER(10, -7)*C39*C41)/(2*C40) * 1000</f>
-        <v>7.7568778610453437</v>
       </c>
     </row>
     <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39">
-        <v>70</v>
-      </c>
-      <c r="F39" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>5</v>
-      </c>
-      <c r="I39">
-        <v>10</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="C39" s="1">
+        <f>$C$40/POWER(1+(POWER(C37/100, 2)/POWER($C$43, 2)), 1.5)</f>
+        <v>7.7568778610453437</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" ref="D39:W39" si="5">$C$40/POWER(1+(POWER(D37/100, 2)/POWER($C$43, 2)), 1.5)</f>
+        <v>7.6617021130409011</v>
+      </c>
+      <c r="E39" s="1">
+        <f t="shared" si="5"/>
+        <v>7.3875424446409612</v>
+      </c>
+      <c r="F39" s="1">
+        <f t="shared" si="5"/>
+        <v>6.9654628481359468</v>
+      </c>
+      <c r="G39" s="1">
+        <f t="shared" si="5"/>
+        <v>6.4384919625856183</v>
+      </c>
+      <c r="H39" s="1">
+        <f t="shared" si="5"/>
+        <v>5.8524232226751316</v>
+      </c>
+      <c r="I39" s="1">
+        <f t="shared" si="5"/>
+        <v>5.2482622725844976</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="5"/>
+        <v>4.6579157240299827</v>
+      </c>
+      <c r="K39" s="1">
+        <f t="shared" si="5"/>
+        <v>4.1030557316699907</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" si="5"/>
+        <v>3.5961512920284524</v>
+      </c>
+      <c r="M39" s="1">
+        <f t="shared" si="5"/>
+        <v>3.1425094915513876</v>
+      </c>
+      <c r="N39" s="1">
+        <f t="shared" si="5"/>
+        <v>2.7424704681904823</v>
+      </c>
+      <c r="O39" s="1">
+        <f t="shared" si="5"/>
+        <v>2.393294802808394</v>
+      </c>
+      <c r="P39" s="1">
+        <f t="shared" si="5"/>
+        <v>2.0905858750120658</v>
+      </c>
+      <c r="Q39" s="1">
+        <f t="shared" si="5"/>
+        <v>1.8292628533410984</v>
+      </c>
+      <c r="R39" s="1">
+        <f t="shared" si="5"/>
+        <v>1.6041717368106754</v>
+      </c>
+      <c r="S39" s="1">
+        <f t="shared" si="5"/>
+        <v>1.410434697484104</v>
+      </c>
+      <c r="T39" s="1">
+        <f t="shared" si="5"/>
+        <v>1.2436243690615909</v>
+      </c>
+      <c r="U39" s="1">
+        <f t="shared" si="5"/>
+        <v>1.0998285575528679</v>
+      </c>
+      <c r="V39" s="1">
+        <f t="shared" si="5"/>
+        <v>0.97565090394196352</v>
+      </c>
+      <c r="W39" s="1">
+        <f t="shared" si="5"/>
+        <v>0.86817729480338701</v>
       </c>
     </row>
     <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40">
+        <f>(4 * PI() * POWER(10, -7)*C42*C44)/(2*C43) * 1000</f>
+        <v>7.7568778610453437</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42">
+        <v>70</v>
+      </c>
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>5</v>
+      </c>
+      <c r="I42">
+        <v>10</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
         <v>13</v>
       </c>
-      <c r="C40">
+      <c r="C43">
         <f>B3/2/1000</f>
         <v>5.5E-2</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F43" t="s">
         <v>8</v>
       </c>
-      <c r="G40">
+      <c r="G43">
         <v>-370</v>
       </c>
-      <c r="H40">
+      <c r="H43">
         <v>-8.1</v>
       </c>
-      <c r="I40">
+      <c r="I43">
         <v>-6.37</v>
       </c>
-      <c r="J40">
+      <c r="J43">
         <v>-67.2</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
         <v>14</v>
       </c>
-      <c r="C41">
+      <c r="C44">
         <v>9.6999999999999993</v>
       </c>
     </row>

--- a/lab3/I14243.xlsx
+++ b/lab3/I14243.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dkomeza/Desktop/Fizyka-Lab/lab3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C186806F-6C01-1245-BA06-DAE97DF8BFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840BF9ED-C84E-E643-89B2-AD9B6CF1CD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{57C4C638-7895-C144-878A-17F30D214164}"/>
   </bookViews>
@@ -16,27 +16,31 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$12</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$A$13</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$B$10:$L$10</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$B$12:$L$12</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$B$13:$L$13</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$B$14:$L$14</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$A$12</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$A$13</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$A$14</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$B$10:$L$10</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$B$12:$L$12</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$B$13:$L$13</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$A$14</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$B$14:$L$14</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$10:$L$10</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$12:$L$12</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$13:$L$13</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$B$14:$L$14</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$A$12</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$A$13</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$A$14</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$36</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$37</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$B$36</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$B$37</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$C$34:$W$34</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$C$36:$W$36</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$C$37:$W$37</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$B$36</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$B$37</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$C$34:$W$34</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$C$36:$W$36</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$C$37:$W$37</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$C$34:$W$34</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$B$36</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Sheet1!$B$37</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">Sheet1!$C$34:$W$34</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">Sheet1!$C$36:$W$36</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Sheet1!$C$37:$W$37</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$C$36:$W$36</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$C$37:$W$37</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$36</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$B$37</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$C$34:$W$34</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$C$36:$W$36</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$C$37:$W$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>liczba zwojów</t>
   </si>
@@ -108,9 +112,6 @@
   </si>
   <si>
     <t>Napięcie U [mV]</t>
-  </si>
-  <si>
-    <t>Indukcja B</t>
   </si>
   <si>
     <t>kolega wylaczyl zasilanie</t>
@@ -151,6 +152,33 @@
   <si>
     <t>c_avg</t>
   </si>
+  <si>
+    <t>r_5</t>
+  </si>
+  <si>
+    <t>r_14</t>
+  </si>
+  <si>
+    <t>r_10</t>
+  </si>
+  <si>
+    <t>1/(c*I)</t>
+  </si>
+  <si>
+    <t>R/c</t>
+  </si>
+  <si>
+    <t>Indukcja B_t [mT]</t>
+  </si>
+  <si>
+    <t>[T/V]</t>
+  </si>
+  <si>
+    <t>Indukcja B_rz [mT]</t>
+  </si>
+  <si>
+    <t>Indukcja [mT]</t>
+  </si>
 </sst>
 </file>
 
@@ -188,10 +216,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1038,7 +1066,1130 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Zależność B[mT]</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> w zależności od odległości od środka cewki</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$36</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Indukcja B_t [mT]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$34:$W$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$36:$W$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>7.7568778610453437</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.6617021130409011</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.3875424446409612</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.9654628481359468</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.4384919625856183</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.8524232226751316</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.2482622725844976</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.6579157240299827</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.1030557316699907</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.5961512920284524</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.1425094915513876</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.7424704681904823</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.393294802808394</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.0905858750120658</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.8292628533410984</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.6041717368106754</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.410434697484104</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.2436243690615909</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.0998285575528679</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.97565090394196352</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.86817729480338701</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BDF9-BD43-A8C9-5BD712D42E78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Indukcja B_rz [mT]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$34:$W$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$37:$W$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>6.5891647553625479</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.4391123697014949</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.1840233140777041</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.7413687763775982</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2837090001113864</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.7360177924485427</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.13580824980433</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.5881170421414863</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.100446788743064</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.6127765353446417</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.1401115205123245</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.7424726985105337</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.3898495922070588</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0822422016018995</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.8121479074120046</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.5945719482034777</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.42201170469326632</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.074739582318847</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.037226485903584</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.92468719665779409</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.88717410024253107</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BDF9-BD43-A8C9-5BD712D42E78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="842417472"/>
+        <c:axId val="842419264"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="842417472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="842419264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="842419264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="842417472"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$42</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Indukcja [mT]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$40:$J$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$42:$J$42</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>273.37107379174722</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46.19176190091288</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8512819380716872</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.55332880210357871</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AD9F-0B48-B01E-66FAF87B8ACB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1069439552"/>
+        <c:axId val="1069441344"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1069439552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1069441344"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1069441344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1069439552"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1581,6 +2732,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1593,7 +3776,7 @@
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>776941</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>89647</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1614,6 +3797,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>807039</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>4232</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>120885</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>27019</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EAC684D-2DBA-41B6-965D-78012BAF5677}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>889000</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>5509</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>29072</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>162806</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A7C051E-CD12-3E5F-8DA9-5D3E29CC43F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1925,7 +4180,8 @@
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -2002,19 +4258,19 @@
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -2131,553 +4387,525 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <f>B12/1000</f>
-        <v>-1.4499999999999999E-3</v>
-      </c>
-      <c r="C15">
-        <f t="shared" ref="C15:L15" si="0">C12/1000</f>
-        <v>-1.06E-3</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>-6.7000000000000002E-4</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>-2.5000000000000001E-4</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>1.1999999999999999E-4</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="0"/>
-        <v>8.7000000000000001E-4</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="0"/>
-        <v>1.2600000000000001E-3</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="0"/>
-        <v>1.64E-3</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>2.0099999999999996E-3</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="0"/>
-        <v>2.3700000000000001E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>10</v>
-      </c>
-      <c r="B16">
-        <f t="shared" ref="B16:L16" si="1">B13/1000</f>
-        <v>-4.7000000000000002E-3</v>
-      </c>
-      <c r="C16">
-        <f t="shared" si="1"/>
-        <v>-3.8E-3</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="1"/>
-        <v>-3.2000000000000002E-3</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>-2.4199999999999998E-3</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>-1.6000000000000001E-3</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>-8.1999999999999998E-4</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>-1E-4</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>5.4000000000000001E-4</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>1.2600000000000001E-3</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="1"/>
-        <v>2.7499999999999998E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B17">
-        <f t="shared" ref="B17:L17" si="2">B14/1000</f>
-        <v>-6.0000000000000001E-3</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="2"/>
-        <v>-4.3E-3</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="2"/>
-        <v>-3.4300000000000003E-3</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="2"/>
-        <v>-2.4500000000000004E-3</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="2"/>
-        <v>-1.3799999999999999E-3</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="2"/>
-        <v>-4.4999999999999999E-4</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="2"/>
-        <v>5.5000000000000003E-4</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="2"/>
-        <v>1.5499999999999999E-3</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="2"/>
-        <v>2.5499999999999997E-3</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="2"/>
-        <v>3.5600000000000002E-3</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="2"/>
-        <v>4.5199999999999997E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="B15" s="2">
         <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * B10) / ($B$3) * 1000</f>
         <v>0</v>
       </c>
-      <c r="C18" s="3">
-        <f t="shared" ref="C18:L18" si="3" xml:space="preserve"> (4*PI()*10^-7 * $A$3 * C10) / ($B$3) * 1000</f>
+      <c r="C15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * C10) / ($B$3) * 1000</f>
         <v>7.9967813000467473E-4</v>
       </c>
-      <c r="D18" s="3">
-        <f t="shared" si="3"/>
+      <c r="D15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * D10) / ($B$3) * 1000</f>
         <v>1.5993562600093495E-3</v>
       </c>
-      <c r="E18" s="3">
-        <f t="shared" si="3"/>
+      <c r="E15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * E10) / ($B$3) * 1000</f>
         <v>2.3990343900140237E-3</v>
       </c>
-      <c r="F18" s="3">
-        <f t="shared" si="3"/>
+      <c r="F15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * F10) / ($B$3) * 1000</f>
         <v>3.1987125200186989E-3</v>
       </c>
-      <c r="G18" s="3">
-        <f t="shared" si="3"/>
+      <c r="G15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * G10) / ($B$3) * 1000</f>
         <v>3.9983906500233729E-3</v>
       </c>
-      <c r="H18" s="3">
-        <f t="shared" si="3"/>
+      <c r="H15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * H10) / ($B$3) * 1000</f>
         <v>4.7980687800280473E-3</v>
       </c>
-      <c r="I18" s="3">
-        <f t="shared" si="3"/>
+      <c r="I15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * I10) / ($B$3) * 1000</f>
         <v>5.5977469100327226E-3</v>
       </c>
-      <c r="J18" s="3">
-        <f t="shared" si="3"/>
+      <c r="J15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * J10) / ($B$3) * 1000</f>
         <v>6.3174572270369303E-3</v>
       </c>
-      <c r="K18" s="3">
-        <f t="shared" si="3"/>
+      <c r="K15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * K10) / ($B$3) * 1000</f>
         <v>7.0371675440411372E-3</v>
       </c>
-      <c r="L18" s="3">
-        <f t="shared" si="3"/>
+      <c r="L15" s="2">
+        <f xml:space="preserve"> (4*PI()*10^-7 * $A$3 * L10) / ($B$3) * 1000</f>
         <v>7.7568778610453441E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <f>SLOPE(B12:L12,$B$15:$L$15)</f>
+        <v>489.84703443408409</v>
+      </c>
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22">
+        <f>B22/A12</f>
+        <v>97.969406886816813</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B25">
-        <f>SLOPE(B12:L12,$B$18:$L$18)</f>
-        <v>489.84703443408409</v>
-      </c>
+      <c r="B23">
+        <f>SLOPE(B13:L13,$B$15:$L$15)</f>
+        <v>945.84212420725271</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <f>B23/A13</f>
+        <v>94.584212420725265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <f>SLOPE(B14:L14,$B$15:$L$15)</f>
+        <v>1302.8528664306698</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <f>B24/A14</f>
+        <v>93.060919030762122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25">
+        <f>AVERAGE(D22:D24)</f>
+        <v>95.204846112768067</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" cm="1">
+        <f t="array" ref="B27:C27">LINEST(B12:L12,$B$10:$L$10,TRUE,FALSE)</f>
+        <v>0.39171996048458391</v>
+      </c>
+      <c r="C27">
+        <v>-1.4517787136692153</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="1">
+        <f>(B27*($B$3/1000))/(A12*4*PI()*10^-7*$A$3)</f>
+        <v>97.969406886816842</v>
+      </c>
+      <c r="F27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27">
+        <f>C27/A12</f>
+        <v>-0.29035574273384307</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" cm="1">
+        <f t="array" ref="B28:C28">LINEST(B13:L13,$B$10:$L$10,TRUE,FALSE)</f>
+        <v>0.75636926116570491</v>
+      </c>
+      <c r="C28">
+        <v>-4.6578625279467598</v>
+      </c>
+      <c r="D28" t="s">
         <v>19</v>
       </c>
-      <c r="D25">
-        <f>B25/A12</f>
-        <v>97.969406886816813</v>
+      <c r="E28" s="1">
+        <f>(B28*($B$3/1000))/(A13*4*PI()*10^-7*$A$3)</f>
+        <v>94.584212420725251</v>
+      </c>
+      <c r="F28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28">
+        <f>C28/A13</f>
+        <v>-0.465786252794676</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>17</v>
       </c>
-      <c r="B26">
-        <f>SLOPE(B13:L13,$B$18:$L$18)</f>
-        <v>945.84212420725271</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B29" cm="1">
+        <f t="array" ref="B29:C29">LINEST(B14:L14,$B$10:$L$10,TRUE,FALSE)</f>
+        <v>1.0418629438985079</v>
+      </c>
+      <c r="C29">
+        <v>-5.63248583164353</v>
+      </c>
+      <c r="D29" t="s">
         <v>20</v>
       </c>
-      <c r="D26">
-        <f>B26/A13</f>
-        <v>94.584212420725265</v>
+      <c r="E29" s="1">
+        <f>(B29*($B$3/1000))/(A14*4*PI()*10^-7*$A$3)</f>
+        <v>93.060919030762108</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29">
+        <f>C29/A14</f>
+        <v>-0.40232041654596645</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27">
-        <f>SLOPE(B14:L14,$B$18:$L$18)</f>
-        <v>1302.8528664306698</v>
-      </c>
-      <c r="C27" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
         <v>21</v>
       </c>
-      <c r="D27">
-        <f>B27/A14</f>
-        <v>93.060919030762122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28">
-        <f>AVERAGE(D25:D27)</f>
+      <c r="E30">
+        <f>AVERAGE(E27:E29)</f>
         <v>95.204846112768067</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" cm="1">
-        <f t="array" ref="B30:C30">LINEST(B15:L15,$B$10:$L$10,TRUE,FALSE)</f>
-        <v>3.917199604845838E-4</v>
-      </c>
-      <c r="C30">
-        <v>-1.4517787136692148E-3</v>
-      </c>
-      <c r="D30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30">
-        <f>B30/A12</f>
-        <v>7.8343992096916763E-5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" cm="1">
-        <f t="array" ref="B31:C31">LINEST(B16:L16,$B$10:$L$10,TRUE,FALSE)</f>
-        <v>7.5636926116570485E-4</v>
-      </c>
-      <c r="C31">
-        <v>-4.6578625279467588E-3</v>
-      </c>
-      <c r="D31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31">
-        <f t="shared" ref="E31:E32" si="4">B31/A13</f>
-        <v>7.5636926116570482E-5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" cm="1">
-        <f t="array" ref="B32:C32">LINEST(B17:L17,$B$10:$L$10,TRUE,FALSE)</f>
-        <v>1.0418629438985077E-3</v>
-      </c>
-      <c r="C32">
-        <v>-5.6324858316435305E-3</v>
-      </c>
-      <c r="D32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32">
-        <f t="shared" si="4"/>
-        <v>7.4418781707036264E-5</v>
       </c>
     </row>
     <row r="33" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="D33" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33">
-        <f>AVERAGE(E30:E32)</f>
-        <v>7.613323330684117E-5</v>
+      <c r="S33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0.5</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>1.5</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>2.5</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>3.5</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34">
+        <v>4.5</v>
+      </c>
+      <c r="M34">
+        <v>5</v>
+      </c>
+      <c r="N34">
+        <v>5.5</v>
+      </c>
+      <c r="O34">
+        <v>6</v>
+      </c>
+      <c r="P34">
+        <v>6.5</v>
+      </c>
+      <c r="Q34">
+        <v>7</v>
+      </c>
+      <c r="R34">
+        <v>7.5</v>
+      </c>
+      <c r="S34">
+        <v>8</v>
+      </c>
+      <c r="T34">
+        <v>8.5</v>
+      </c>
+      <c r="U34">
+        <v>9</v>
+      </c>
+      <c r="V34">
+        <v>9.5</v>
+      </c>
+      <c r="W34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>3.15</v>
+      </c>
+      <c r="D35">
+        <v>2.95</v>
+      </c>
+      <c r="E35">
+        <v>2.61</v>
+      </c>
+      <c r="F35">
+        <v>2.02</v>
+      </c>
+      <c r="G35">
+        <v>1.41</v>
+      </c>
+      <c r="H35">
+        <v>0.68</v>
+      </c>
+      <c r="I35">
+        <v>-0.12</v>
+      </c>
+      <c r="J35">
+        <v>-0.85</v>
+      </c>
+      <c r="K35">
+        <v>-1.5</v>
+      </c>
+      <c r="L35">
+        <v>-2.15</v>
+      </c>
+      <c r="M35">
+        <v>-2.78</v>
+      </c>
+      <c r="N35">
+        <v>-3.31</v>
+      </c>
+      <c r="O35">
+        <f>-3.78</f>
+        <v>-3.78</v>
+      </c>
+      <c r="P35">
+        <v>-4.1900000000000004</v>
+      </c>
+      <c r="Q35">
+        <v>-4.55</v>
+      </c>
+      <c r="R35">
+        <v>-4.84</v>
+      </c>
+      <c r="S35">
+        <v>-5.07</v>
+      </c>
+      <c r="T35">
+        <v>-4.2</v>
+      </c>
+      <c r="U35">
+        <v>-4.25</v>
+      </c>
+      <c r="V35">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="W35">
+        <v>-4.45</v>
       </c>
     </row>
     <row r="36" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="S36" t="s">
-        <v>10</v>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="1">
+        <f>$C$38/POWER(1+(POWER(C34/100, 2)/POWER($C$41, 2)), 1.5)</f>
+        <v>7.7568778610453437</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" ref="D36:W36" si="0">$C$38/POWER(1+(POWER(D34/100, 2)/POWER($C$41, 2)), 1.5)</f>
+        <v>7.6617021130409011</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="0"/>
+        <v>7.3875424446409612</v>
+      </c>
+      <c r="F36" s="1">
+        <f t="shared" si="0"/>
+        <v>6.9654628481359468</v>
+      </c>
+      <c r="G36" s="1">
+        <f t="shared" si="0"/>
+        <v>6.4384919625856183</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="0"/>
+        <v>5.8524232226751316</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="0"/>
+        <v>5.2482622725844976</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="0"/>
+        <v>4.6579157240299827</v>
+      </c>
+      <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>4.1030557316699907</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="0"/>
+        <v>3.5961512920284524</v>
+      </c>
+      <c r="M36" s="1">
+        <f t="shared" si="0"/>
+        <v>3.1425094915513876</v>
+      </c>
+      <c r="N36" s="1">
+        <f t="shared" si="0"/>
+        <v>2.7424704681904823</v>
+      </c>
+      <c r="O36" s="1">
+        <f t="shared" si="0"/>
+        <v>2.393294802808394</v>
+      </c>
+      <c r="P36" s="1">
+        <f t="shared" si="0"/>
+        <v>2.0905858750120658</v>
+      </c>
+      <c r="Q36" s="1">
+        <f t="shared" si="0"/>
+        <v>1.8292628533410984</v>
+      </c>
+      <c r="R36" s="1">
+        <f t="shared" si="0"/>
+        <v>1.6041717368106754</v>
+      </c>
+      <c r="S36" s="1">
+        <f t="shared" si="0"/>
+        <v>1.410434697484104</v>
+      </c>
+      <c r="T36" s="1">
+        <f t="shared" si="0"/>
+        <v>1.2436243690615909</v>
+      </c>
+      <c r="U36" s="1">
+        <f t="shared" si="0"/>
+        <v>1.0998285575528679</v>
+      </c>
+      <c r="V36" s="1">
+        <f t="shared" si="0"/>
+        <v>0.97565090394196352</v>
+      </c>
+      <c r="W36" s="1">
+        <f t="shared" si="0"/>
+        <v>0.86817729480338701</v>
       </c>
     </row>
     <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0.5</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>1.5</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-      <c r="H37">
-        <v>2.5</v>
-      </c>
-      <c r="I37">
-        <v>3</v>
-      </c>
-      <c r="J37">
-        <v>3.5</v>
-      </c>
-      <c r="K37">
-        <v>4</v>
-      </c>
-      <c r="L37">
-        <v>4.5</v>
-      </c>
-      <c r="M37">
-        <v>5</v>
-      </c>
-      <c r="N37">
-        <v>5.5</v>
-      </c>
-      <c r="O37">
-        <v>6</v>
-      </c>
-      <c r="P37">
-        <v>6.5</v>
-      </c>
-      <c r="Q37">
-        <v>7</v>
-      </c>
-      <c r="R37">
-        <v>7.5</v>
-      </c>
-      <c r="S37">
-        <v>8</v>
-      </c>
-      <c r="T37">
-        <v>8.5</v>
-      </c>
-      <c r="U37">
-        <v>9</v>
-      </c>
-      <c r="V37">
-        <v>9.5</v>
-      </c>
-      <c r="W37">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="C37" s="1">
+        <f>(C35*$C$43)-$C$44 * 1000</f>
+        <v>6.5891647553625479</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" ref="D37:W37" si="1">(D35*$C$43)-$C$44 * 1000</f>
+        <v>6.4391123697014949</v>
+      </c>
+      <c r="E37" s="1">
+        <f t="shared" si="1"/>
+        <v>6.1840233140777041</v>
+      </c>
+      <c r="F37" s="1">
+        <f t="shared" si="1"/>
+        <v>5.7413687763775982</v>
+      </c>
+      <c r="G37" s="1">
+        <f t="shared" si="1"/>
+        <v>5.2837090001113864</v>
+      </c>
+      <c r="H37" s="1">
+        <f t="shared" si="1"/>
+        <v>4.7360177924485427</v>
+      </c>
+      <c r="I37" s="1">
+        <f t="shared" si="1"/>
+        <v>4.13580824980433</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="1"/>
+        <v>3.5881170421414863</v>
+      </c>
+      <c r="K37" s="1">
+        <f t="shared" si="1"/>
+        <v>3.100446788743064</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="1"/>
+        <v>2.6127765353446417</v>
+      </c>
+      <c r="M37" s="1">
+        <f t="shared" si="1"/>
+        <v>2.1401115205123245</v>
+      </c>
+      <c r="N37" s="1">
+        <f t="shared" si="1"/>
+        <v>1.7424726985105337</v>
+      </c>
+      <c r="O37" s="1">
+        <f t="shared" si="1"/>
+        <v>1.3898495922070588</v>
+      </c>
+      <c r="P37" s="1">
+        <f t="shared" si="1"/>
+        <v>1.0822422016018995</v>
+      </c>
+      <c r="Q37" s="1">
+        <f t="shared" si="1"/>
+        <v>0.8121479074120046</v>
+      </c>
+      <c r="R37" s="1">
+        <f t="shared" si="1"/>
+        <v>0.5945719482034777</v>
+      </c>
+      <c r="S37" s="1">
+        <f t="shared" si="1"/>
+        <v>0.42201170469326632</v>
+      </c>
+      <c r="T37" s="1">
+        <f t="shared" si="1"/>
+        <v>1.074739582318847</v>
+      </c>
+      <c r="U37" s="1">
+        <f t="shared" si="1"/>
+        <v>1.037226485903584</v>
+      </c>
+      <c r="V37" s="1">
+        <f t="shared" si="1"/>
+        <v>0.92468719665779409</v>
+      </c>
+      <c r="W37" s="1">
+        <f t="shared" si="1"/>
+        <v>0.88717410024253107</v>
       </c>
     </row>
     <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>3.15</v>
-      </c>
-      <c r="D38">
-        <v>2.95</v>
-      </c>
-      <c r="E38">
-        <v>2.61</v>
-      </c>
-      <c r="F38">
-        <v>2.02</v>
-      </c>
-      <c r="G38">
-        <v>1.41</v>
-      </c>
-      <c r="H38">
-        <v>0.68</v>
-      </c>
-      <c r="I38">
-        <v>-0.12</v>
-      </c>
-      <c r="J38">
-        <v>-0.85</v>
-      </c>
-      <c r="K38">
-        <v>-1.5</v>
-      </c>
-      <c r="L38">
-        <v>-2.15</v>
-      </c>
-      <c r="M38">
-        <v>-2.78</v>
-      </c>
-      <c r="N38">
-        <v>-3.31</v>
-      </c>
-      <c r="O38">
-        <f>--3.78</f>
-        <v>3.78</v>
-      </c>
-      <c r="P38">
-        <v>-4.1900000000000004</v>
-      </c>
-      <c r="Q38">
-        <v>-4.55</v>
-      </c>
-      <c r="R38">
-        <v>-4.84</v>
-      </c>
-      <c r="S38">
-        <v>-5.07</v>
-      </c>
-      <c r="T38">
-        <v>-4.2</v>
-      </c>
-      <c r="U38">
-        <v>-4.25</v>
-      </c>
-      <c r="V38">
-        <v>-4.4000000000000004</v>
-      </c>
-      <c r="W38">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="1">
-        <f>$C$40/POWER(1+(POWER(C37/100, 2)/POWER($C$43, 2)), 1.5)</f>
+        <f>(4 * PI() * POWER(10, -7)*C40*C42)/(2*C41) * 1000</f>
         <v>7.7568778610453437</v>
-      </c>
-      <c r="D39" s="1">
-        <f t="shared" ref="D39:W39" si="5">$C$40/POWER(1+(POWER(D37/100, 2)/POWER($C$43, 2)), 1.5)</f>
-        <v>7.6617021130409011</v>
-      </c>
-      <c r="E39" s="1">
-        <f t="shared" si="5"/>
-        <v>7.3875424446409612</v>
-      </c>
-      <c r="F39" s="1">
-        <f t="shared" si="5"/>
-        <v>6.9654628481359468</v>
-      </c>
-      <c r="G39" s="1">
-        <f t="shared" si="5"/>
-        <v>6.4384919625856183</v>
-      </c>
-      <c r="H39" s="1">
-        <f t="shared" si="5"/>
-        <v>5.8524232226751316</v>
-      </c>
-      <c r="I39" s="1">
-        <f t="shared" si="5"/>
-        <v>5.2482622725844976</v>
-      </c>
-      <c r="J39" s="1">
-        <f t="shared" si="5"/>
-        <v>4.6579157240299827</v>
-      </c>
-      <c r="K39" s="1">
-        <f t="shared" si="5"/>
-        <v>4.1030557316699907</v>
-      </c>
-      <c r="L39" s="1">
-        <f t="shared" si="5"/>
-        <v>3.5961512920284524</v>
-      </c>
-      <c r="M39" s="1">
-        <f t="shared" si="5"/>
-        <v>3.1425094915513876</v>
-      </c>
-      <c r="N39" s="1">
-        <f t="shared" si="5"/>
-        <v>2.7424704681904823</v>
-      </c>
-      <c r="O39" s="1">
-        <f t="shared" si="5"/>
-        <v>2.393294802808394</v>
-      </c>
-      <c r="P39" s="1">
-        <f t="shared" si="5"/>
-        <v>2.0905858750120658</v>
-      </c>
-      <c r="Q39" s="1">
-        <f t="shared" si="5"/>
-        <v>1.8292628533410984</v>
-      </c>
-      <c r="R39" s="1">
-        <f t="shared" si="5"/>
-        <v>1.6041717368106754</v>
-      </c>
-      <c r="S39" s="1">
-        <f t="shared" si="5"/>
-        <v>1.410434697484104</v>
-      </c>
-      <c r="T39" s="1">
-        <f t="shared" si="5"/>
-        <v>1.2436243690615909</v>
-      </c>
-      <c r="U39" s="1">
-        <f t="shared" si="5"/>
-        <v>1.0998285575528679</v>
-      </c>
-      <c r="V39" s="1">
-        <f t="shared" si="5"/>
-        <v>0.97565090394196352</v>
-      </c>
-      <c r="W39" s="1">
-        <f t="shared" si="5"/>
-        <v>0.86817729480338701</v>
       </c>
     </row>
     <row r="40" spans="2:23" x14ac:dyDescent="0.2">
@@ -2685,63 +4913,94 @@
         <v>11</v>
       </c>
       <c r="C40">
-        <f>(4 * PI() * POWER(10, -7)*C42*C44)/(2*C43) * 1000</f>
-        <v>7.7568778610453437</v>
+        <v>70</v>
+      </c>
+      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+      <c r="J40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41">
+        <f>B3/2/1000</f>
+        <v>5.5E-2</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41">
+        <v>-370</v>
+      </c>
+      <c r="H41">
+        <v>-67.2</v>
+      </c>
+      <c r="I41">
+        <v>-8.1</v>
+      </c>
+      <c r="J41">
+        <v>-6.37</v>
       </c>
     </row>
     <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42">
-        <v>70</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>5</v>
-      </c>
-      <c r="I42">
-        <v>10</v>
-      </c>
-      <c r="J42">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="G42" s="1">
+        <f>ABS((G41*$C$43)-$C$44 * 1000)</f>
+        <v>273.37107379174722</v>
+      </c>
+      <c r="H42" s="1">
+        <f t="shared" ref="H42:J42" si="2">ABS((H41*$C$43)-$C$44 * 1000)</f>
+        <v>46.19176190091288</v>
+      </c>
+      <c r="I42" s="1">
+        <f t="shared" si="2"/>
+        <v>1.8512819380716872</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="2"/>
+        <v>0.55332880210357871</v>
       </c>
     </row>
     <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C43">
-        <f>B3/2/1000</f>
-        <v>5.5E-2</v>
-      </c>
-      <c r="F43" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43">
-        <v>-370</v>
-      </c>
-      <c r="H43">
-        <v>-8.1</v>
-      </c>
-      <c r="I43">
-        <v>-6.37</v>
-      </c>
-      <c r="J43">
-        <v>-67.2</v>
+        <f>1/(E30*(14/1000))</f>
+        <v>0.75026192830526539</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C44">
-        <v>9.6999999999999993</v>
+        <f>G29/E30</f>
+        <v>-4.2258396812009623E-3</v>
       </c>
     </row>
   </sheetData>

--- a/lab3/I14243.xlsx
+++ b/lab3/I14243.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dkomeza/Desktop/Fizyka-Lab/lab3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840BF9ED-C84E-E643-89B2-AD9B6CF1CD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622D23DB-485F-BD43-8A8E-E29251A6705E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{57C4C638-7895-C144-878A-17F30D214164}"/>
   </bookViews>
